--- a/prix/rexuo.xlsx
+++ b/prix/rexuo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A965A6D-09F5-4682-A695-7180C217A62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6542436D-6BAA-4480-937E-F50AA0C19C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
@@ -245,10 +245,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">

--- a/prix/rexuo.xlsx
+++ b/prix/rexuo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6542436D-6BAA-4480-937E-F50AA0C19C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE35A0A3-7262-4E55-90B3-FD65DB5DF342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
@@ -244,10 +244,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -637,13 +637,13 @@
       <c r="C2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>30.84</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -657,13 +657,13 @@
       <c r="C3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>43.61</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="11">
         <v>3</v>
       </c>
     </row>
@@ -677,14 +677,14 @@
       <c r="C4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>38.01</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="10">
-        <v>12</v>
+      <c r="F4" s="11">
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -697,13 +697,13 @@
       <c r="C5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>63.050000000000004</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="11">
         <v>9</v>
       </c>
     </row>
@@ -714,13 +714,13 @@
       <c r="C6" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="10">
         <v>24.28</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="11">
         <v>10</v>
       </c>
     </row>
@@ -734,14 +734,14 @@
       <c r="C7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>12.98</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="10">
-        <v>19</v>
+      <c r="F7" s="11">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -754,13 +754,13 @@
       <c r="C8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>19.490000000000002</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="11">
         <v>50</v>
       </c>
     </row>
@@ -774,13 +774,13 @@
       <c r="C9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>15.030000000000001</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="11">
         <v>5</v>
       </c>
     </row>
@@ -794,14 +794,14 @@
       <c r="C10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>24.96</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="10">
-        <v>3</v>
+      <c r="F10" s="11">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -814,13 +814,13 @@
       <c r="C11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>18.05</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="11">
         <v>4</v>
       </c>
     </row>
@@ -834,13 +834,13 @@
       <c r="C12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="10">
         <v>30.66</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="11">
         <v>5</v>
       </c>
     </row>

--- a/prix/rexuo.xlsx
+++ b/prix/rexuo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE35A0A3-7262-4E55-90B3-FD65DB5DF342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DF06C8-2ED9-409D-9B13-2051E1D145D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>

--- a/prix/rexuo.xlsx
+++ b/prix/rexuo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DF06C8-2ED9-409D-9B13-2051E1D145D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C5F116-2EFD-429F-9B63-498C19DC0168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
@@ -781,7 +781,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">

--- a/prix/rexuo.xlsx
+++ b/prix/rexuo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\raccords-plomberie\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C5F116-2EFD-429F-9B63-498C19DC0168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46F0EC94-72F1-4305-80C0-F5B65A1E9367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{4E6DADB0-7397-45D0-B450-49581E83838D}"/>
   </bookViews>
